--- a/branches/chore/dedupe-skills-into-catalog/all-profiles.xlsx
+++ b/branches/chore/dedupe-skills-into-catalog/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:35:20+00:00</t>
+    <t>2026-08-06T13:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/dedupe-skills-into-catalog/all-profiles.xlsx
+++ b/branches/chore/dedupe-skills-into-catalog/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:30:11+00:00</t>
+    <t>2026-08-07T06:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
